--- a/Codelist Excel Files and Conversion Templates to XML/columnType.xlsx
+++ b/Codelist Excel Files and Conversion Templates to XML/columnType.xlsx
@@ -2109,77 +2109,176 @@
         <f>IF(ISNA(VLOOKUP(B24,Definitions!B$2:B$1839,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
-      <c r="B24" s="2" t="n"/>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>simple_bored</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>//diggs:RISystemBasis/diggs:riTechniqueType</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25">
         <f>IF(ISNA(VLOOKUP(B25,Definitions!B$2:B$1839,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
-      <c r="B25" s="2" t="n"/>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>bored_with_casing</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>//diggs:RISystemBasis/diggs:riTechniqueType</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26">
         <f>IF(ISNA(VLOOKUP(B26,Definitions!B$2:B$1839,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
-      <c r="B26" s="2" t="n"/>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>bored_with_slurry</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>//diggs:RISystemBasis/diggs:riTechniqueType</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27">
         <f>IF(ISNA(VLOOKUP(B27,Definitions!B$2:B$1839,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
-      <c r="B27" s="13" t="n"/>
+      <c r="B27" s="13" t="inlineStr">
+        <is>
+          <t>continuous_flight_hollow_auger</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>//diggs:RISystemBasis/diggs:riTechniqueType</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28">
         <f>IF(ISNA(VLOOKUP(B28,Definitions!B$2:B$1839,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
-      <c r="B28" s="13" t="n"/>
+      <c r="B28" s="13" t="inlineStr">
+        <is>
+          <t>micropile</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>//diggs:RISystemBasis/diggs:riTechniqueType</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29">
         <f>IF(ISNA(VLOOKUP(B29,Definitions!B$2:B$1839,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
-      <c r="B29" s="13" t="n"/>
+      <c r="B29" s="13" t="inlineStr">
+        <is>
+          <t>cip_vibro_driven</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>//diggs:RISystemBasis/diggs:riTechniqueType</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30">
         <f>IF(ISNA(VLOOKUP(B30,Definitions!B$2:B$1839,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
-      <c r="B30" s="13" t="n"/>
+      <c r="B30" s="13" t="inlineStr">
+        <is>
+          <t>cip_driven</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>//diggs:RISystemBasis/diggs:riTechniqueType</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31">
         <f>IF(ISNA(VLOOKUP(B31,Definitions!B$2:B$1839,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
-      <c r="B31" s="13" t="n"/>
+      <c r="B31" s="13" t="inlineStr">
+        <is>
+          <t>prefab_vibro_driven</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>//diggs:RISystemBasis/diggs:riTechniqueType</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32">
         <f>IF(ISNA(VLOOKUP(B32,Definitions!B$2:B$1839,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
-      <c r="B32" s="13" t="n"/>
+      <c r="B32" s="13" t="inlineStr">
+        <is>
+          <t>prefab_driven</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>//diggs:RISystemBasis/diggs:riTechniqueType</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33">
         <f>IF(ISNA(VLOOKUP(B33,Definitions!B$2:B$1839,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
-      <c r="B33" s="13" t="n"/>
+      <c r="B33" s="13" t="inlineStr">
+        <is>
+          <t>soil_mixing</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>//diggs:RISystemBasis/diggs:riTechniqueType</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34">
         <f>IF(ISNA(VLOOKUP(B34,Definitions!B$2:B$1839,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
-      <c r="B34" s="13" t="n"/>
+      <c r="B34" s="13" t="inlineStr">
+        <is>
+          <t>jet_grouting</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>//diggs:RISystemBasis/diggs:riTechniqueType</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35">

--- a/Codelist Excel Files and Conversion Templates to XML/columnType.xlsx
+++ b/Codelist Excel Files and Conversion Templates to XML/columnType.xlsx
@@ -985,7 +985,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Codes naming the rigid inclusion installation technique family, shared by the design/specification intent (diggs:RIColumnSpecification/columnType) and the as-built record (diggs:RigidInclusion/columnType) so that design and as-built do not drift into different vocabularies for the same concept. Derived from the eleven-value installationType list carried by the retired CMCArrayType sketch (diggs-schema commit 0254e97, RigidInclusions.xsd, pre-C4 retirement). The list is open: technique families proliferate under proprietary trade names and cannot be closed.</t>
+          <t>Codes naming the rigid inclusion installation technique family, shared by the design/specification intent (diggs:RIColumnSpecification/columnType) and the as-built record (diggs:RIColumn/columnType) so that design and as-built do not drift into different vocabularies for the same concept. Derived from the eleven-value installationType list carried by the retired CMCArrayType sketch (diggs-schema commit 0254e97, RigidInclusions.xsd, pre-C4 retirement). The list is open: technique families proliferate under proprietary trade names and cannot be closed.</t>
         </is>
       </c>
     </row>
@@ -1764,7 +1764,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>//diggs:RigidInclusion/diggs:columnType</t>
+          <t>//diggs:RIColumn/diggs:columnType</t>
         </is>
       </c>
     </row>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>//diggs:RigidInclusion/diggs:columnType</t>
+          <t>//diggs:RIColumn/diggs:columnType</t>
         </is>
       </c>
     </row>
@@ -1828,7 +1828,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>//diggs:RigidInclusion/diggs:columnType</t>
+          <t>//diggs:RIColumn/diggs:columnType</t>
         </is>
       </c>
     </row>
@@ -1860,7 +1860,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>//diggs:RigidInclusion/diggs:columnType</t>
+          <t>//diggs:RIColumn/diggs:columnType</t>
         </is>
       </c>
     </row>
@@ -1892,7 +1892,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>//diggs:RigidInclusion/diggs:columnType</t>
+          <t>//diggs:RIColumn/diggs:columnType</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>//diggs:RigidInclusion/diggs:columnType</t>
+          <t>//diggs:RIColumn/diggs:columnType</t>
         </is>
       </c>
     </row>
@@ -1956,7 +1956,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>//diggs:RigidInclusion/diggs:columnType</t>
+          <t>//diggs:RIColumn/diggs:columnType</t>
         </is>
       </c>
     </row>
@@ -1988,7 +1988,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>//diggs:RigidInclusion/diggs:columnType</t>
+          <t>//diggs:RIColumn/diggs:columnType</t>
         </is>
       </c>
     </row>
@@ -2020,7 +2020,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>//diggs:RigidInclusion/diggs:columnType</t>
+          <t>//diggs:RIColumn/diggs:columnType</t>
         </is>
       </c>
     </row>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>//diggs:RigidInclusion/diggs:columnType</t>
+          <t>//diggs:RIColumn/diggs:columnType</t>
         </is>
       </c>
     </row>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>//diggs:RigidInclusion/diggs:columnType</t>
+          <t>//diggs:RIColumn/diggs:columnType</t>
         </is>
       </c>
     </row>

--- a/Codelist Excel Files and Conversion Templates to XML/columnType.xlsx
+++ b/Codelist Excel Files and Conversion Templates to XML/columnType.xlsx
@@ -2116,7 +2116,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>//diggs:RISystemBasis/diggs:riTechniqueType</t>
+          <t>//diggs:RIProgramBasis/diggs:riTechniqueType</t>
         </is>
       </c>
     </row>
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>//diggs:RISystemBasis/diggs:riTechniqueType</t>
+          <t>//diggs:RIProgramBasis/diggs:riTechniqueType</t>
         </is>
       </c>
     </row>
@@ -2148,7 +2148,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>//diggs:RISystemBasis/diggs:riTechniqueType</t>
+          <t>//diggs:RIProgramBasis/diggs:riTechniqueType</t>
         </is>
       </c>
     </row>
@@ -2164,7 +2164,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>//diggs:RISystemBasis/diggs:riTechniqueType</t>
+          <t>//diggs:RIProgramBasis/diggs:riTechniqueType</t>
         </is>
       </c>
     </row>
@@ -2180,7 +2180,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>//diggs:RISystemBasis/diggs:riTechniqueType</t>
+          <t>//diggs:RIProgramBasis/diggs:riTechniqueType</t>
         </is>
       </c>
     </row>
@@ -2196,7 +2196,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>//diggs:RISystemBasis/diggs:riTechniqueType</t>
+          <t>//diggs:RIProgramBasis/diggs:riTechniqueType</t>
         </is>
       </c>
     </row>
@@ -2212,7 +2212,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>//diggs:RISystemBasis/diggs:riTechniqueType</t>
+          <t>//diggs:RIProgramBasis/diggs:riTechniqueType</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>//diggs:RISystemBasis/diggs:riTechniqueType</t>
+          <t>//diggs:RIProgramBasis/diggs:riTechniqueType</t>
         </is>
       </c>
     </row>
@@ -2244,7 +2244,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>//diggs:RISystemBasis/diggs:riTechniqueType</t>
+          <t>//diggs:RIProgramBasis/diggs:riTechniqueType</t>
         </is>
       </c>
     </row>
@@ -2260,7 +2260,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>//diggs:RISystemBasis/diggs:riTechniqueType</t>
+          <t>//diggs:RIProgramBasis/diggs:riTechniqueType</t>
         </is>
       </c>
     </row>
@@ -2276,7 +2276,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>//diggs:RISystemBasis/diggs:riTechniqueType</t>
+          <t>//diggs:RIProgramBasis/diggs:riTechniqueType</t>
         </is>
       </c>
     </row>

--- a/Codelist Excel Files and Conversion Templates to XML/columnType.xlsx
+++ b/Codelist Excel Files and Conversion Templates to XML/columnType.xlsx
@@ -1087,7 +1087,7 @@
       </c>
       <c r="D2" s="14" t="inlineStr">
         <is>
-          <t>A column installed by simple rotary boring/drilling with no casing or slurry support.</t>
+          <t>A column installed by simple rotary boring/drilling with no casing or slurry support. Replacement family: soil is removed as the column is formed.</t>
         </is>
       </c>
       <c r="E2" s="13" t="inlineStr">
@@ -1119,7 +1119,7 @@
       </c>
       <c r="D3" s="14" t="inlineStr">
         <is>
-          <t>A column installed by rotary boring with temporary or permanent casing supporting the borehole.</t>
+          <t>A column installed by rotary boring with temporary or permanent casing supporting the borehole. Replacement family: soil is removed as the column is formed.</t>
         </is>
       </c>
       <c r="E3" s="13" t="inlineStr">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>A column installed by rotary boring with slurry (e.g. bentonite or polymer) supporting the borehole.</t>
+          <t>A column installed by rotary boring with slurry (e.g. bentonite or polymer) supporting the borehole. Replacement family: soil is removed as the column is formed.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1182,7 +1182,7 @@
       </c>
       <c r="D5" s="14" t="inlineStr">
         <is>
-          <t>A column installed with a continuous-flight hollow-stem auger, concrete or grout placed through the auger stem as it is withdrawn.</t>
+          <t>A column installed with a continuous-flight hollow-stem auger, concrete or grout placed through the auger stem as it is withdrawn. Replacement family: soil is removed as the column is formed. Commonly abbreviated CFA; auger cast-in-place (ACIP) is a closely related replacement technique.</t>
         </is>
       </c>
       <c r="E5" s="13" t="inlineStr">
@@ -1245,7 +1245,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>A column formed by driving a closed-end casing or mandrel with a vibratory hammer and casting concrete in place.</t>
+          <t>A column formed by driving a closed-end casing or mandrel with a vibratory hammer and casting concrete in place. Displacement family: soil is displaced laterally rather than removed, so no spoil is generated.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1276,7 +1276,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>A column formed by driving a closed-end casing or mandrel with an impact hammer and casting concrete in place.</t>
+          <t>A column formed by driving a closed-end casing or mandrel with an impact hammer and casting concrete in place. Displacement family: soil is displaced laterally rather than removed, so no spoil is generated.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -1307,7 +1307,7 @@
       </c>
       <c r="D9" s="16" t="inlineStr">
         <is>
-          <t>A prefabricated (precast or steel) column installed by vibratory driving.</t>
+          <t>A prefabricated (precast or steel) column installed by vibratory driving. Displacement family: soil is displaced laterally rather than removed, so no spoil is generated.</t>
         </is>
       </c>
       <c r="E9" s="17" t="inlineStr">
@@ -1338,7 +1338,7 @@
       </c>
       <c r="D10" s="14" t="inlineStr">
         <is>
-          <t>A prefabricated (precast or steel) column installed by impact driving.</t>
+          <t>A prefabricated (precast or steel) column installed by impact driving. Displacement family: soil is displaced laterally rather than removed, so no spoil is generated.</t>
         </is>
       </c>
       <c r="E10" s="13" t="inlineStr">
@@ -1422,24 +1422,64 @@
         <f>IF(ISNA(VLOOKUP(B13,AssociatedElements!B$2:B2951,1,FALSE)),"Not used","")</f>
         <v/>
       </c>
-      <c r="B13" s="13" t="n"/>
-      <c r="C13" s="13" t="n"/>
-      <c r="D13" s="14" t="n"/>
-      <c r="E13" s="13" t="n"/>
+      <c r="B13" s="13" t="inlineStr">
+        <is>
+          <t>grouted_stone_column</t>
+        </is>
+      </c>
+      <c r="C13" s="13" t="inlineStr">
+        <is>
+          <t>Grouted stone/gravel column</t>
+        </is>
+      </c>
+      <c r="D13" s="14" t="inlineStr">
+        <is>
+          <t>A column formed from stone or gravel that is grouted to give it rigidity, intermediate between an unbound aggregate pier and a fully cemented inclusion.</t>
+        </is>
+      </c>
+      <c r="E13" s="13" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
       <c r="F13" s="13" t="n"/>
-      <c r="G13" s="9" t="n"/>
+      <c r="G13" s="9" t="inlineStr">
+        <is>
+          <t>DIGGS</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2">
         <f>IF(ISNA(VLOOKUP(B14,AssociatedElements!B$2:B2952,1,FALSE)),"Not used","")</f>
         <v/>
       </c>
-      <c r="B14" s="13" t="n"/>
-      <c r="C14" s="13" t="n"/>
-      <c r="D14" s="14" t="n"/>
-      <c r="E14" s="13" t="n"/>
+      <c r="B14" s="13" t="inlineStr">
+        <is>
+          <t>vibro_concrete_column</t>
+        </is>
+      </c>
+      <c r="C14" s="13" t="inlineStr">
+        <is>
+          <t>Vibro concrete column (VCC)</t>
+        </is>
+      </c>
+      <c r="D14" s="14" t="inlineStr">
+        <is>
+          <t>A column formed by advancing a vibratory probe and placing concrete through it. Displacement family: soil is displaced laterally rather than removed, so no spoil is generated.</t>
+        </is>
+      </c>
+      <c r="E14" s="13" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
       <c r="F14" s="13" t="n"/>
-      <c r="G14" s="9" t="n"/>
+      <c r="G14" s="9" t="inlineStr">
+        <is>
+          <t>DIGGS</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2">
@@ -1721,7 +1761,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D37"/>
+  <dimension ref="A1:D40"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="16"/>
   <cols>
     <col width="6.83203125" customWidth="1" min="1" max="1"/>
@@ -2285,21 +2325,84 @@
         <f>IF(ISNA(VLOOKUP(B35,Definitions!B$2:B$1839,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
-      <c r="B35" s="13" t="n"/>
+      <c r="B35" s="13" t="inlineStr">
+        <is>
+          <t>grouted_stone_column</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>//diggs:RIColumn/diggs:columnType</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36">
         <f>IF(ISNA(VLOOKUP(B36,Definitions!B$2:B$1839,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
-      <c r="B36" s="13" t="n"/>
+      <c r="B36" s="13" t="inlineStr">
+        <is>
+          <t>grouted_stone_column</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>//diggs:RIColumnSpecification/diggs:columnType</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37">
         <f>IF(ISNA(VLOOKUP(B37,Definitions!B$2:B$1839,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
-      <c r="B37" s="2" t="n"/>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>grouted_stone_column</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>//diggs:RIProgramBasis/diggs:riTechniqueType</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>vibro_concrete_column</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>//diggs:RIColumn/diggs:columnType</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>vibro_concrete_column</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>//diggs:RIColumnSpecification/diggs:columnType</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>vibro_concrete_column</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>//diggs:RIProgramBasis/diggs:riTechniqueType</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Codelist Excel Files and Conversion Templates to XML/columnType.xlsx
+++ b/Codelist Excel Files and Conversion Templates to XML/columnType.xlsx
@@ -1014,7 +1014,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H37"/>
+  <dimension ref="A1:H35"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="16"/>
   <cols>
     <col width="7" customWidth="1" style="2" min="1" max="1"/>
@@ -1087,7 +1087,7 @@
       </c>
       <c r="D2" s="14" t="inlineStr">
         <is>
-          <t>A column installed by simple rotary boring/drilling with no casing or slurry support. Replacement family: soil is removed as the column is formed.</t>
+          <t>A column installed by simple rotary boring/drilling with no casing or slurry support.</t>
         </is>
       </c>
       <c r="E2" s="13" t="inlineStr">
@@ -1119,7 +1119,7 @@
       </c>
       <c r="D3" s="14" t="inlineStr">
         <is>
-          <t>A column installed by rotary boring with temporary or permanent casing supporting the borehole. Replacement family: soil is removed as the column is formed.</t>
+          <t>A column installed by rotary boring with temporary or permanent casing supporting the borehole.</t>
         </is>
       </c>
       <c r="E3" s="13" t="inlineStr">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>A column installed by rotary boring with slurry (e.g. bentonite or polymer) supporting the borehole. Replacement family: soil is removed as the column is formed.</t>
+          <t>A column installed by rotary boring with slurry (e.g. bentonite or polymer) supporting the borehole.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1182,7 +1182,7 @@
       </c>
       <c r="D5" s="14" t="inlineStr">
         <is>
-          <t>A column installed with a continuous-flight hollow-stem auger, concrete or grout placed through the auger stem as it is withdrawn. Replacement family: soil is removed as the column is formed. Commonly abbreviated CFA; auger cast-in-place (ACIP) is a closely related replacement technique.</t>
+          <t>A column installed with a continuous-flight hollow-stem auger, concrete or grout placed through the auger stem as it is withdrawn. Commonly abbreviated CFA; auger cast-in-place (ACIP) is a closely related replacement technique.</t>
         </is>
       </c>
       <c r="E5" s="13" t="inlineStr">
@@ -1245,7 +1245,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>A column formed by driving a closed-end casing or mandrel with a vibratory hammer and casting concrete in place. Displacement family: soil is displaced laterally rather than removed, so no spoil is generated.</t>
+          <t>A column formed by driving a closed-end casing or mandrel with a vibratory hammer and casting concrete in place.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1276,7 +1276,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>A column formed by driving a closed-end casing or mandrel with an impact hammer and casting concrete in place. Displacement family: soil is displaced laterally rather than removed, so no spoil is generated.</t>
+          <t>A column formed by driving a closed-end casing or mandrel with an impact hammer and casting concrete in place.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -1307,7 +1307,7 @@
       </c>
       <c r="D9" s="16" t="inlineStr">
         <is>
-          <t>A prefabricated (precast or steel) column installed by vibratory driving. Displacement family: soil is displaced laterally rather than removed, so no spoil is generated.</t>
+          <t>A prefabricated (precast or steel) column installed by vibratory driving.</t>
         </is>
       </c>
       <c r="E9" s="17" t="inlineStr">
@@ -1338,7 +1338,7 @@
       </c>
       <c r="D10" s="14" t="inlineStr">
         <is>
-          <t>A prefabricated (precast or steel) column installed by impact driving. Displacement family: soil is displaced laterally rather than removed, so no spoil is generated.</t>
+          <t>A prefabricated (precast or steel) column installed by impact driving.</t>
         </is>
       </c>
       <c r="E10" s="13" t="inlineStr">
@@ -1355,22 +1355,22 @@
     </row>
     <row r="11">
       <c r="A11" s="2">
-        <f>IF(ISNA(VLOOKUP(B11,AssociatedElements!B$2:B2949,1,FALSE)),"Not used","")</f>
+        <f>IF(ISNA(VLOOKUP(B13,AssociatedElements!B$2:B2951,1,FALSE)),"Not used","")</f>
         <v/>
       </c>
       <c r="B11" s="13" t="inlineStr">
         <is>
-          <t>soil_mixing</t>
+          <t>grouted_stone_column</t>
         </is>
       </c>
       <c r="C11" s="13" t="inlineStr">
         <is>
-          <t>Soil mixing</t>
+          <t>Grouted stone/gravel column</t>
         </is>
       </c>
       <c r="D11" s="14" t="inlineStr">
         <is>
-          <t>A column formed by in-situ mechanical or auger mixing of the native soil with a cementitious binder.</t>
+          <t>A column formed from stone or gravel that is grouted to give it rigidity, intermediate between an unbound aggregate pier and a fully cemented inclusion.</t>
         </is>
       </c>
       <c r="E11" s="13" t="inlineStr">
@@ -1387,22 +1387,22 @@
     </row>
     <row r="12">
       <c r="A12" s="2">
-        <f>IF(ISNA(VLOOKUP(B12,AssociatedElements!B$2:B2950,1,FALSE)),"Not used","")</f>
+        <f>IF(ISNA(VLOOKUP(B14,AssociatedElements!B$2:B2952,1,FALSE)),"Not used","")</f>
         <v/>
       </c>
       <c r="B12" s="13" t="inlineStr">
         <is>
-          <t>jet_grouting</t>
+          <t>vibro_concrete_column</t>
         </is>
       </c>
       <c r="C12" s="13" t="inlineStr">
         <is>
-          <t>Jet grouting</t>
+          <t>Vibro concrete column (VCC)</t>
         </is>
       </c>
       <c r="D12" s="14" t="inlineStr">
         <is>
-          <t>A column formed by high-pressure erosion and mixing of the native soil with cementitious grout injected through a jetting tool.</t>
+          <t>A column formed by advancing a vibratory probe and placing concrete through it.</t>
         </is>
       </c>
       <c r="E12" s="13" t="inlineStr">
@@ -1419,30 +1419,30 @@
     </row>
     <row r="13">
       <c r="A13" s="2">
-        <f>IF(ISNA(VLOOKUP(B13,AssociatedElements!B$2:B2951,1,FALSE)),"Not used","")</f>
+        <f>IF(ISNA(VLOOKUP(B15,AssociatedElements!B$2:B2953,1,FALSE)),"Not used","")</f>
         <v/>
       </c>
       <c r="B13" s="13" t="inlineStr">
         <is>
-          <t>grouted_stone_column</t>
-        </is>
-      </c>
-      <c r="C13" s="13" t="inlineStr">
-        <is>
-          <t>Grouted stone/gravel column</t>
-        </is>
-      </c>
-      <c r="D13" s="14" t="inlineStr">
-        <is>
-          <t>A column formed from stone or gravel that is grouted to give it rigidity, intermediate between an unbound aggregate pier and a fully cemented inclusion.</t>
-        </is>
-      </c>
-      <c r="E13" s="13" t="inlineStr">
+          <t>drilled_displacement_column</t>
+        </is>
+      </c>
+      <c r="C13" s="18" t="inlineStr">
+        <is>
+          <t>Drilled displacement column</t>
+        </is>
+      </c>
+      <c r="D13" s="19" t="inlineStr">
+        <is>
+          <t>A column formed by a shaped displacement tool advanced with a rotary action, which pushes soil radially outward instead of removing it, and through which concrete or grout is placed as the tool is withdrawn. The most widely used rigid inclusion technique. Trade names in common use: Controlled Modulus Column (CMC, Menard); and Rigid Inclusion (RI), also marketed as GI, GeoConcrete Column (GCC), Controlled Stiffness Column (CSC) and Augered Pressure Grout Column (APGC) by Keller / Hayward Baker. Distinct from continuous_flight_hollow_auger, which removes spoil and is therefore a replacement technique.</t>
+        </is>
+      </c>
+      <c r="E13" s="18" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="F13" s="13" t="n"/>
+      <c r="F13" s="18" t="n"/>
       <c r="G13" s="9" t="inlineStr">
         <is>
           <t>DIGGS</t>
@@ -1451,39 +1451,19 @@
     </row>
     <row r="14">
       <c r="A14" s="2">
-        <f>IF(ISNA(VLOOKUP(B14,AssociatedElements!B$2:B2952,1,FALSE)),"Not used","")</f>
+        <f>IF(ISNA(VLOOKUP(B16,AssociatedElements!B$2:B2954,1,FALSE)),"Not used","")</f>
         <v/>
       </c>
-      <c r="B14" s="13" t="inlineStr">
-        <is>
-          <t>vibro_concrete_column</t>
-        </is>
-      </c>
-      <c r="C14" s="13" t="inlineStr">
-        <is>
-          <t>Vibro concrete column (VCC)</t>
-        </is>
-      </c>
-      <c r="D14" s="14" t="inlineStr">
-        <is>
-          <t>A column formed by advancing a vibratory probe and placing concrete through it. Displacement family: soil is displaced laterally rather than removed, so no spoil is generated.</t>
-        </is>
-      </c>
-      <c r="E14" s="13" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="F14" s="13" t="n"/>
-      <c r="G14" s="9" t="inlineStr">
-        <is>
-          <t>DIGGS</t>
-        </is>
-      </c>
+      <c r="B14" s="13" t="n"/>
+      <c r="C14" s="18" t="n"/>
+      <c r="D14" s="19" t="n"/>
+      <c r="E14" s="18" t="n"/>
+      <c r="F14" s="18" t="n"/>
+      <c r="G14" s="9" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="2">
-        <f>IF(ISNA(VLOOKUP(B15,AssociatedElements!B$2:B2953,1,FALSE)),"Not used","")</f>
+        <f>IF(ISNA(VLOOKUP(B17,AssociatedElements!B$2:B2955,1,FALSE)),"Not used","")</f>
         <v/>
       </c>
       <c r="B15" s="13" t="n"/>
@@ -1495,7 +1475,7 @@
     </row>
     <row r="16">
       <c r="A16" s="2">
-        <f>IF(ISNA(VLOOKUP(B16,AssociatedElements!B$2:B2954,1,FALSE)),"Not used","")</f>
+        <f>IF(ISNA(VLOOKUP(B18,AssociatedElements!B$2:B2956,1,FALSE)),"Not used","")</f>
         <v/>
       </c>
       <c r="B16" s="13" t="n"/>
@@ -1507,7 +1487,7 @@
     </row>
     <row r="17">
       <c r="A17" s="2">
-        <f>IF(ISNA(VLOOKUP(B17,AssociatedElements!B$2:B2955,1,FALSE)),"Not used","")</f>
+        <f>IF(ISNA(VLOOKUP(B19,AssociatedElements!B$2:B2957,1,FALSE)),"Not used","")</f>
         <v/>
       </c>
       <c r="B17" s="13" t="n"/>
@@ -1519,7 +1499,7 @@
     </row>
     <row r="18">
       <c r="A18" s="2">
-        <f>IF(ISNA(VLOOKUP(B18,AssociatedElements!B$2:B2956,1,FALSE)),"Not used","")</f>
+        <f>IF(ISNA(VLOOKUP(B20,AssociatedElements!B$2:B2958,1,FALSE)),"Not used","")</f>
         <v/>
       </c>
       <c r="B18" s="13" t="n"/>
@@ -1531,7 +1511,7 @@
     </row>
     <row r="19">
       <c r="A19" s="2">
-        <f>IF(ISNA(VLOOKUP(B19,AssociatedElements!B$2:B2957,1,FALSE)),"Not used","")</f>
+        <f>IF(ISNA(VLOOKUP(B21,AssociatedElements!B$2:B2959,1,FALSE)),"Not used","")</f>
         <v/>
       </c>
       <c r="B19" s="13" t="n"/>
@@ -1543,7 +1523,7 @@
     </row>
     <row r="20">
       <c r="A20" s="2">
-        <f>IF(ISNA(VLOOKUP(B20,AssociatedElements!B$2:B2958,1,FALSE)),"Not used","")</f>
+        <f>IF(ISNA(VLOOKUP(B22,AssociatedElements!B$2:B2960,1,FALSE)),"Not used","")</f>
         <v/>
       </c>
       <c r="B20" s="13" t="n"/>
@@ -1555,7 +1535,7 @@
     </row>
     <row r="21">
       <c r="A21" s="2">
-        <f>IF(ISNA(VLOOKUP(B21,AssociatedElements!B$2:B2959,1,FALSE)),"Not used","")</f>
+        <f>IF(ISNA(VLOOKUP(B23,AssociatedElements!B$2:B2961,1,FALSE)),"Not used","")</f>
         <v/>
       </c>
       <c r="B21" s="13" t="n"/>
@@ -1567,73 +1547,73 @@
     </row>
     <row r="22">
       <c r="A22" s="2">
-        <f>IF(ISNA(VLOOKUP(B22,AssociatedElements!B$2:B2960,1,FALSE)),"Not used","")</f>
+        <f>IF(ISNA(VLOOKUP(B24,AssociatedElements!B$2:B2962,1,FALSE)),"Not used","")</f>
         <v/>
       </c>
-      <c r="B22" s="13" t="n"/>
-      <c r="C22" s="18" t="n"/>
-      <c r="D22" s="19" t="n"/>
-      <c r="E22" s="18" t="n"/>
-      <c r="F22" s="18" t="n"/>
+      <c r="D22" s="16" t="n"/>
       <c r="G22" s="9" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="2">
-        <f>IF(ISNA(VLOOKUP(B23,AssociatedElements!B$2:B2961,1,FALSE)),"Not used","")</f>
+        <f>IF(ISNA(VLOOKUP(B25,AssociatedElements!B$2:B2963,1,FALSE)),"Not used","")</f>
         <v/>
       </c>
       <c r="B23" s="13" t="n"/>
-      <c r="C23" s="18" t="n"/>
-      <c r="D23" s="19" t="n"/>
-      <c r="E23" s="18" t="n"/>
-      <c r="F23" s="18" t="n"/>
+      <c r="C23" s="13" t="n"/>
+      <c r="E23" s="13" t="n"/>
+      <c r="F23" s="13" t="n"/>
       <c r="G23" s="9" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="2">
-        <f>IF(ISNA(VLOOKUP(B24,AssociatedElements!B$2:B2962,1,FALSE)),"Not used","")</f>
+        <f>IF(ISNA(VLOOKUP(B26,AssociatedElements!B$2:B2964,1,FALSE)),"Not used","")</f>
         <v/>
       </c>
-      <c r="D24" s="16" t="n"/>
+      <c r="B24" s="13" t="n"/>
+      <c r="C24" s="13" t="n"/>
+      <c r="E24" s="13" t="n"/>
+      <c r="F24" s="13" t="n"/>
       <c r="G24" s="9" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="2">
-        <f>IF(ISNA(VLOOKUP(B25,AssociatedElements!B$2:B2963,1,FALSE)),"Not used","")</f>
+        <f>IF(ISNA(VLOOKUP(B27,AssociatedElements!B$2:B2965,1,FALSE)),"Not used","")</f>
         <v/>
       </c>
       <c r="B25" s="13" t="n"/>
       <c r="C25" s="13" t="n"/>
+      <c r="D25" s="15" t="n"/>
       <c r="E25" s="13" t="n"/>
       <c r="F25" s="13" t="n"/>
       <c r="G25" s="9" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="2">
-        <f>IF(ISNA(VLOOKUP(B26,AssociatedElements!B$2:B2964,1,FALSE)),"Not used","")</f>
+        <f>IF(ISNA(VLOOKUP(B28,AssociatedElements!B$2:B2966,1,FALSE)),"Not used","")</f>
         <v/>
       </c>
       <c r="B26" s="13" t="n"/>
       <c r="C26" s="13" t="n"/>
+      <c r="D26" s="14" t="n"/>
       <c r="E26" s="13" t="n"/>
       <c r="F26" s="13" t="n"/>
       <c r="G26" s="9" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="2">
-        <f>IF(ISNA(VLOOKUP(B27,AssociatedElements!B$2:B2965,1,FALSE)),"Not used","")</f>
+        <f>IF(ISNA(VLOOKUP(B29,AssociatedElements!B$2:B2967,1,FALSE)),"Not used","")</f>
         <v/>
       </c>
       <c r="B27" s="13" t="n"/>
       <c r="C27" s="13" t="n"/>
-      <c r="D27" s="15" t="n"/>
+      <c r="D27" s="14" t="n"/>
       <c r="E27" s="13" t="n"/>
       <c r="F27" s="13" t="n"/>
       <c r="G27" s="9" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="2">
-        <f>IF(ISNA(VLOOKUP(B28,AssociatedElements!B$2:B2966,1,FALSE)),"Not used","")</f>
+        <f>IF(ISNA(VLOOKUP(B30,AssociatedElements!B$2:B2968,1,FALSE)),"Not used","")</f>
         <v/>
       </c>
       <c r="B28" s="13" t="n"/>
@@ -1645,31 +1625,31 @@
     </row>
     <row r="29">
       <c r="A29" s="2">
-        <f>IF(ISNA(VLOOKUP(B29,AssociatedElements!B$2:B2967,1,FALSE)),"Not used","")</f>
+        <f>IF(ISNA(VLOOKUP(B31,AssociatedElements!B$2:B2969,1,FALSE)),"Not used","")</f>
         <v/>
       </c>
       <c r="B29" s="13" t="n"/>
-      <c r="C29" s="13" t="n"/>
-      <c r="D29" s="14" t="n"/>
-      <c r="E29" s="13" t="n"/>
-      <c r="F29" s="13" t="n"/>
+      <c r="C29" s="18" t="n"/>
+      <c r="D29" s="19" t="n"/>
+      <c r="E29" s="18" t="n"/>
+      <c r="F29" s="18" t="n"/>
       <c r="G29" s="9" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="2">
-        <f>IF(ISNA(VLOOKUP(B30,AssociatedElements!B$2:B2968,1,FALSE)),"Not used","")</f>
+        <f>IF(ISNA(VLOOKUP(B32,AssociatedElements!B$2:B2970,1,FALSE)),"Not used","")</f>
         <v/>
       </c>
       <c r="B30" s="13" t="n"/>
-      <c r="C30" s="13" t="n"/>
-      <c r="D30" s="14" t="n"/>
-      <c r="E30" s="13" t="n"/>
-      <c r="F30" s="13" t="n"/>
+      <c r="C30" s="18" t="n"/>
+      <c r="D30" s="19" t="n"/>
+      <c r="E30" s="18" t="n"/>
+      <c r="F30" s="18" t="n"/>
       <c r="G30" s="9" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="2">
-        <f>IF(ISNA(VLOOKUP(B31,AssociatedElements!B$2:B2969,1,FALSE)),"Not used","")</f>
+        <f>IF(ISNA(VLOOKUP(B33,AssociatedElements!B$2:B2971,1,FALSE)),"Not used","")</f>
         <v/>
       </c>
       <c r="B31" s="13" t="n"/>
@@ -1681,7 +1661,7 @@
     </row>
     <row r="32">
       <c r="A32" s="2">
-        <f>IF(ISNA(VLOOKUP(B32,AssociatedElements!B$2:B2970,1,FALSE)),"Not used","")</f>
+        <f>IF(ISNA(VLOOKUP(B34,AssociatedElements!B$2:B2972,1,FALSE)),"Not used","")</f>
         <v/>
       </c>
       <c r="B32" s="13" t="n"/>
@@ -1693,7 +1673,7 @@
     </row>
     <row r="33">
       <c r="A33" s="2">
-        <f>IF(ISNA(VLOOKUP(B33,AssociatedElements!B$2:B2971,1,FALSE)),"Not used","")</f>
+        <f>IF(ISNA(VLOOKUP(B35,AssociatedElements!B$2:B2973,1,FALSE)),"Not used","")</f>
         <v/>
       </c>
       <c r="B33" s="13" t="n"/>
@@ -1705,7 +1685,7 @@
     </row>
     <row r="34">
       <c r="A34" s="2">
-        <f>IF(ISNA(VLOOKUP(B34,AssociatedElements!B$2:B2972,1,FALSE)),"Not used","")</f>
+        <f>IF(ISNA(VLOOKUP(B36,AssociatedElements!B$2:B2974,1,FALSE)),"Not used","")</f>
         <v/>
       </c>
       <c r="B34" s="13" t="n"/>
@@ -1717,34 +1697,10 @@
     </row>
     <row r="35">
       <c r="A35" s="2">
-        <f>IF(ISNA(VLOOKUP(B35,AssociatedElements!B$2:B2973,1,FALSE)),"Not used","")</f>
-        <v/>
-      </c>
-      <c r="B35" s="13" t="n"/>
-      <c r="C35" s="18" t="n"/>
-      <c r="D35" s="19" t="n"/>
-      <c r="E35" s="18" t="n"/>
-      <c r="F35" s="18" t="n"/>
-      <c r="G35" s="9" t="n"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="2">
-        <f>IF(ISNA(VLOOKUP(B36,AssociatedElements!B$2:B2974,1,FALSE)),"Not used","")</f>
-        <v/>
-      </c>
-      <c r="B36" s="13" t="n"/>
-      <c r="C36" s="18" t="n"/>
-      <c r="D36" s="19" t="n"/>
-      <c r="E36" s="18" t="n"/>
-      <c r="F36" s="18" t="n"/>
-      <c r="G36" s="9" t="n"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="2">
         <f>IF(ISNA(VLOOKUP(B37,AssociatedElements!B$2:B2975,1,FALSE)),"Not used","")</f>
         <v/>
       </c>
-      <c r="G37" s="9" t="n"/>
+      <c r="G35" s="9" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1761,7 +1717,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D40"/>
+  <dimension ref="A1:D25"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="16"/>
   <cols>
     <col width="6.83203125" customWidth="1" min="1" max="1"/>
@@ -1793,11 +1749,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2">
-        <f>IF(ISNA(VLOOKUP(#REF!,Definitions!B$2:B$1839,1,FALSE)),"Not listed","")</f>
-        <v/>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>simple_bored</t>
         </is>
@@ -1807,13 +1759,14 @@
           <t>//diggs:RIColumn/diggs:columnType</t>
         </is>
       </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:RIColumn/diggs:riInstallationMethod[.='replacement']</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3">
-        <f>IF(ISNA(VLOOKUP(B3,Definitions!B$2:B$1839,1,FALSE)),"Not listed","")</f>
-        <v/>
-      </c>
-      <c r="B3" s="20" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>simple_bored</t>
         </is>
@@ -1823,13 +1776,14 @@
           <t>//diggs:RIColumnSpecification/diggs:columnType</t>
         </is>
       </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:RIColumnSpecification/diggs:riInstallationMethod[.='replacement']</t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="A4">
-        <f>IF(ISNA(VLOOKUP(B4,Definitions!B$2:B$1839,1,FALSE)),"Not listed","")</f>
-        <v/>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>bored_with_casing</t>
         </is>
@@ -1839,13 +1793,14 @@
           <t>//diggs:RIColumn/diggs:columnType</t>
         </is>
       </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:RIColumn/diggs:riInstallationMethod[.='replacement']</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5">
-        <f>IF(ISNA(VLOOKUP(B5,Definitions!B$2:B$1839,1,FALSE)),"Not listed","")</f>
-        <v/>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>bored_with_casing</t>
         </is>
@@ -1855,13 +1810,14 @@
           <t>//diggs:RIColumnSpecification/diggs:columnType</t>
         </is>
       </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:RIColumnSpecification/diggs:riInstallationMethod[.='replacement']</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6">
-        <f>IF(ISNA(VLOOKUP(B6,Definitions!B$2:B$1839,1,FALSE)),"Not listed","")</f>
-        <v/>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>bored_with_slurry</t>
         </is>
@@ -1871,13 +1827,14 @@
           <t>//diggs:RIColumn/diggs:columnType</t>
         </is>
       </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:RIColumn/diggs:riInstallationMethod[.='replacement']</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7">
-        <f>IF(ISNA(VLOOKUP(B7,Definitions!B$2:B$1839,1,FALSE)),"Not listed","")</f>
-        <v/>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>bored_with_slurry</t>
         </is>
@@ -1887,13 +1844,14 @@
           <t>//diggs:RIColumnSpecification/diggs:columnType</t>
         </is>
       </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:RIColumnSpecification/diggs:riInstallationMethod[.='replacement']</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8">
-        <f>IF(ISNA(VLOOKUP(B8,Definitions!B$2:B$1839,1,FALSE)),"Not listed","")</f>
-        <v/>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>continuous_flight_hollow_auger</t>
         </is>
@@ -1903,13 +1861,14 @@
           <t>//diggs:RIColumn/diggs:columnType</t>
         </is>
       </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:RIColumn/diggs:riInstallationMethod[.='replacement']</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9">
-        <f>IF(ISNA(VLOOKUP(B9,Definitions!B$2:B$1839,1,FALSE)),"Not listed","")</f>
-        <v/>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>continuous_flight_hollow_auger</t>
         </is>
@@ -1919,488 +1878,281 @@
           <t>//diggs:RIColumnSpecification/diggs:columnType</t>
         </is>
       </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:RIColumnSpecification/diggs:riInstallationMethod[.='replacement']</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10">
-        <f>IF(ISNA(VLOOKUP(B10,Definitions!B$2:B$1839,1,FALSE)),"Not listed","")</f>
-        <v/>
-      </c>
-      <c r="B10" s="20" t="inlineStr">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>cip_vibro_driven</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>//diggs:RIColumn/diggs:columnType</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:RIColumn/diggs:riInstallationMethod[.='full_displacement']</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>cip_vibro_driven</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>//diggs:RIColumnSpecification/diggs:columnType</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:RIColumnSpecification/diggs:riInstallationMethod[.='full_displacement']</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>cip_driven</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>//diggs:RIColumn/diggs:columnType</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:RIColumn/diggs:riInstallationMethod[.='full_displacement']</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>cip_driven</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>//diggs:RIColumnSpecification/diggs:columnType</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:RIColumnSpecification/diggs:riInstallationMethod[.='full_displacement']</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>prefab_vibro_driven</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>//diggs:RIColumn/diggs:columnType</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:RIColumn/diggs:riInstallationMethod[.='full_displacement']</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>prefab_vibro_driven</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>//diggs:RIColumnSpecification/diggs:columnType</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:RIColumnSpecification/diggs:riInstallationMethod[.='full_displacement']</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>prefab_driven</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>//diggs:RIColumn/diggs:columnType</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:RIColumn/diggs:riInstallationMethod[.='full_displacement']</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>prefab_driven</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>//diggs:RIColumnSpecification/diggs:columnType</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:RIColumnSpecification/diggs:riInstallationMethod[.='full_displacement']</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>vibro_concrete_column</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>//diggs:RIColumn/diggs:columnType</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:RIColumn/diggs:riInstallationMethod[.='full_displacement']</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>vibro_concrete_column</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>//diggs:RIColumnSpecification/diggs:columnType</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:RIColumnSpecification/diggs:riInstallationMethod[.='full_displacement']</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>drilled_displacement_column</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>//diggs:RIColumn/diggs:columnType</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:RIColumn/diggs:riInstallationMethod[.='full_displacement' or .='partial_displacement']</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>drilled_displacement_column</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>//diggs:RIColumnSpecification/diggs:columnType</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:RIColumnSpecification/diggs:riInstallationMethod[.='full_displacement' or .='partial_displacement']</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" t="inlineStr">
         <is>
           <t>micropile</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>//diggs:RIColumn/diggs:columnType</t>
         </is>
       </c>
-    </row>
-    <row r="11">
-      <c r="A11">
-        <f>IF(ISNA(VLOOKUP(B11,Definitions!B$2:B$1839,1,FALSE)),"Not listed","")</f>
-        <v/>
-      </c>
-      <c r="B11" s="20" t="inlineStr">
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:RIColumn/diggs:riInstallationMethod[.='full_displacement' or .='replacement']</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" t="inlineStr">
         <is>
           <t>micropile</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>//diggs:RIColumnSpecification/diggs:columnType</t>
         </is>
       </c>
-    </row>
-    <row r="12">
-      <c r="A12">
-        <f>IF(ISNA(VLOOKUP(B12,Definitions!B$2:B$1839,1,FALSE)),"Not listed","")</f>
-        <v/>
-      </c>
-      <c r="B12" s="20" t="inlineStr">
-        <is>
-          <t>cip_vibro_driven</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:RIColumnSpecification/diggs:riInstallationMethod[.='full_displacement' or .='replacement']</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>grouted_stone_column</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
         <is>
           <t>//diggs:RIColumn/diggs:columnType</t>
         </is>
       </c>
-    </row>
-    <row r="13">
-      <c r="A13">
-        <f>IF(ISNA(VLOOKUP(B13,Definitions!B$2:B$1839,1,FALSE)),"Not listed","")</f>
-        <v/>
-      </c>
-      <c r="B13" s="20" t="inlineStr">
-        <is>
-          <t>cip_vibro_driven</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:RIColumn/diggs:riInstallationMethod[.='full_displacement' or .='replacement']</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>grouted_stone_column</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
         <is>
           <t>//diggs:RIColumnSpecification/diggs:columnType</t>
         </is>
       </c>
-    </row>
-    <row r="14">
-      <c r="A14">
-        <f>IF(ISNA(VLOOKUP(B14,Definitions!B$2:B$1839,1,FALSE)),"Not listed","")</f>
-        <v/>
-      </c>
-      <c r="B14" s="20" t="inlineStr">
-        <is>
-          <t>cip_driven</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>//diggs:RIColumn/diggs:columnType</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15">
-        <f>IF(ISNA(VLOOKUP(B15,Definitions!B$2:B$1839,1,FALSE)),"Not listed","")</f>
-        <v/>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>cip_driven</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>//diggs:RIColumnSpecification/diggs:columnType</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16">
-        <f>IF(ISNA(VLOOKUP(B16,Definitions!B$2:B$1839,1,FALSE)),"Not listed","")</f>
-        <v/>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>prefab_vibro_driven</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>//diggs:RIColumn/diggs:columnType</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17">
-        <f>IF(ISNA(VLOOKUP(B17,Definitions!B$2:B$1839,1,FALSE)),"Not listed","")</f>
-        <v/>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>prefab_vibro_driven</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>//diggs:RIColumnSpecification/diggs:columnType</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18">
-        <f>IF(ISNA(VLOOKUP(B18,Definitions!B$2:B$1839,1,FALSE)),"Not listed","")</f>
-        <v/>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>prefab_driven</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>//diggs:RIColumn/diggs:columnType</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19">
-        <f>IF(ISNA(VLOOKUP(B19,Definitions!B$2:B$1839,1,FALSE)),"Not listed","")</f>
-        <v/>
-      </c>
-      <c r="B19" s="20" t="inlineStr">
-        <is>
-          <t>prefab_driven</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>//diggs:RIColumnSpecification/diggs:columnType</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20">
-        <f>IF(ISNA(VLOOKUP(B20,Definitions!B$2:B$1839,1,FALSE)),"Not listed","")</f>
-        <v/>
-      </c>
-      <c r="B20" s="20" t="inlineStr">
-        <is>
-          <t>soil_mixing</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>//diggs:RIColumn/diggs:columnType</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21">
-        <f>IF(ISNA(VLOOKUP(B21,Definitions!B$2:B$1839,1,FALSE)),"Not listed","")</f>
-        <v/>
-      </c>
-      <c r="B21" s="20" t="inlineStr">
-        <is>
-          <t>soil_mixing</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>//diggs:RIColumnSpecification/diggs:columnType</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22">
-        <f>IF(ISNA(VLOOKUP(B22,Definitions!B$2:B$1839,1,FALSE)),"Not listed","")</f>
-        <v/>
-      </c>
-      <c r="B22" s="20" t="inlineStr">
-        <is>
-          <t>jet_grouting</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>//diggs:RIColumn/diggs:columnType</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23">
-        <f>IF(ISNA(VLOOKUP(B23,Definitions!B$2:B$1839,1,FALSE)),"Not listed","")</f>
-        <v/>
-      </c>
-      <c r="B23" s="20" t="inlineStr">
-        <is>
-          <t>jet_grouting</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>//diggs:RIColumnSpecification/diggs:columnType</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24">
-        <f>IF(ISNA(VLOOKUP(B24,Definitions!B$2:B$1839,1,FALSE)),"Not listed","")</f>
-        <v/>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>simple_bored</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>//diggs:RIProgramBasis/diggs:riTechniqueType</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25">
-        <f>IF(ISNA(VLOOKUP(B25,Definitions!B$2:B$1839,1,FALSE)),"Not listed","")</f>
-        <v/>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>bored_with_casing</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>//diggs:RIProgramBasis/diggs:riTechniqueType</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26">
-        <f>IF(ISNA(VLOOKUP(B26,Definitions!B$2:B$1839,1,FALSE)),"Not listed","")</f>
-        <v/>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>bored_with_slurry</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>//diggs:RIProgramBasis/diggs:riTechniqueType</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27">
-        <f>IF(ISNA(VLOOKUP(B27,Definitions!B$2:B$1839,1,FALSE)),"Not listed","")</f>
-        <v/>
-      </c>
-      <c r="B27" s="13" t="inlineStr">
-        <is>
-          <t>continuous_flight_hollow_auger</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>//diggs:RIProgramBasis/diggs:riTechniqueType</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28">
-        <f>IF(ISNA(VLOOKUP(B28,Definitions!B$2:B$1839,1,FALSE)),"Not listed","")</f>
-        <v/>
-      </c>
-      <c r="B28" s="13" t="inlineStr">
-        <is>
-          <t>micropile</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>//diggs:RIProgramBasis/diggs:riTechniqueType</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29">
-        <f>IF(ISNA(VLOOKUP(B29,Definitions!B$2:B$1839,1,FALSE)),"Not listed","")</f>
-        <v/>
-      </c>
-      <c r="B29" s="13" t="inlineStr">
-        <is>
-          <t>cip_vibro_driven</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>//diggs:RIProgramBasis/diggs:riTechniqueType</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30">
-        <f>IF(ISNA(VLOOKUP(B30,Definitions!B$2:B$1839,1,FALSE)),"Not listed","")</f>
-        <v/>
-      </c>
-      <c r="B30" s="13" t="inlineStr">
-        <is>
-          <t>cip_driven</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>//diggs:RIProgramBasis/diggs:riTechniqueType</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31">
-        <f>IF(ISNA(VLOOKUP(B31,Definitions!B$2:B$1839,1,FALSE)),"Not listed","")</f>
-        <v/>
-      </c>
-      <c r="B31" s="13" t="inlineStr">
-        <is>
-          <t>prefab_vibro_driven</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>//diggs:RIProgramBasis/diggs:riTechniqueType</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32">
-        <f>IF(ISNA(VLOOKUP(B32,Definitions!B$2:B$1839,1,FALSE)),"Not listed","")</f>
-        <v/>
-      </c>
-      <c r="B32" s="13" t="inlineStr">
-        <is>
-          <t>prefab_driven</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>//diggs:RIProgramBasis/diggs:riTechniqueType</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33">
-        <f>IF(ISNA(VLOOKUP(B33,Definitions!B$2:B$1839,1,FALSE)),"Not listed","")</f>
-        <v/>
-      </c>
-      <c r="B33" s="13" t="inlineStr">
-        <is>
-          <t>soil_mixing</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>//diggs:RIProgramBasis/diggs:riTechniqueType</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34">
-        <f>IF(ISNA(VLOOKUP(B34,Definitions!B$2:B$1839,1,FALSE)),"Not listed","")</f>
-        <v/>
-      </c>
-      <c r="B34" s="13" t="inlineStr">
-        <is>
-          <t>jet_grouting</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>//diggs:RIProgramBasis/diggs:riTechniqueType</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35">
-        <f>IF(ISNA(VLOOKUP(B35,Definitions!B$2:B$1839,1,FALSE)),"Not listed","")</f>
-        <v/>
-      </c>
-      <c r="B35" s="13" t="inlineStr">
-        <is>
-          <t>grouted_stone_column</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>//diggs:RIColumn/diggs:columnType</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36">
-        <f>IF(ISNA(VLOOKUP(B36,Definitions!B$2:B$1839,1,FALSE)),"Not listed","")</f>
-        <v/>
-      </c>
-      <c r="B36" s="13" t="inlineStr">
-        <is>
-          <t>grouted_stone_column</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>//diggs:RIColumnSpecification/diggs:columnType</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37">
-        <f>IF(ISNA(VLOOKUP(B37,Definitions!B$2:B$1839,1,FALSE)),"Not listed","")</f>
-        <v/>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>grouted_stone_column</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>//diggs:RIProgramBasis/diggs:riTechniqueType</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>vibro_concrete_column</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>//diggs:RIColumn/diggs:columnType</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>vibro_concrete_column</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>//diggs:RIColumnSpecification/diggs:columnType</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>vibro_concrete_column</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>//diggs:RIProgramBasis/diggs:riTechniqueType</t>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:RIColumnSpecification/diggs:riInstallationMethod[.='full_displacement' or .='replacement']</t>
         </is>
       </c>
     </row>
